--- a/output/stock_quant_scores/AMZN_balance_df.xlsx
+++ b/output/stock_quant_scores/AMZN_balance_df.xlsx
@@ -1483,38 +1483,52 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>116395000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>19314000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>138245000000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>85915000000</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>282304000000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>142266000000</v>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>420549000000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1532,8 +1546,12 @@
         <v>57324000000</v>
       </c>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>161580000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>32640000000</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
@@ -1545,7 +1563,9 @@
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>36220000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
